--- a/output/Seating_Arrangement.xlsx
+++ b/output/Seating_Arrangement.xlsx
@@ -37,10 +37,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Seating Arrangement'!$1:$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Seating Arrangement'!$A$1:$G$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Room Blocks'!$A$12:$I$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Seating Arrangement'!$A$1:$G$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Room Blocks'!$A$12:$I$42</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Room Blocks'!$1:$12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Room Blocks'!$A$1:$I$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Room Blocks'!$A$1:$I$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Allocation Summary'!$A$8:$J$35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Allocation Summary'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Allocation Summary'!$A$1:$J$35</definedName>
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -732,7 +732,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>F.Y. - Regular/Additional Examination</t>
+          <t>Regular/Additional Examination</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -840,7 +840,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>001-014, 016-022, 024-032</t>
+          <t>001-030</t>
         </is>
       </c>
       <c r="G9" s="8" t="n">
@@ -869,7 +869,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>033-062</t>
+          <t>031-060</t>
         </is>
       </c>
       <c r="G10" s="8" t="n">
@@ -898,7 +898,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -908,16 +908,16 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>063-080</t>
+          <t>061-063</t>
         </is>
       </c>
       <c r="G11" s="8" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
@@ -925,26 +925,26 @@
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>V</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>001-008, 010-013</t>
+          <t>1-27</t>
         </is>
       </c>
       <c r="G12" s="8" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
@@ -954,214 +954,190 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>V</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>014-023, 025-048</t>
+          <t>28-51</t>
         </is>
       </c>
       <c r="G13" s="8" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>SYBMS (Finance)</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Cost Accounting I (Minor)</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>1-10</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>SYBMS (Finance)</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Cost Accounting I (Minor)</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>11-24</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>SYBMS (Marketing)</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>SYBMS (Marketing)</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>3-4, 7-14, 19-22, 24, 28-29, 34-35, 40-47, 49, 51-52, 56, 58-59, 61</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>Database Management</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>049-060</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>001-004</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>005-011, 013-035</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>036-040</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>5</v>
-      </c>
-    </row>
     <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="6" t="n"/>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>001-018</t>
-        </is>
-      </c>
+          <t>Unused</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n">
-        <v>8</v>
-      </c>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n"/>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>019-050</t>
-        </is>
-      </c>
+          <t>Unused</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>204</t>
         </is>
       </c>
       <c r="B20" s="7" t="n"/>
@@ -1180,7 +1156,7 @@
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>205</t>
         </is>
       </c>
       <c r="B21" s="7" t="n"/>
@@ -1199,7 +1175,7 @@
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>206</t>
         </is>
       </c>
       <c r="B22" s="7" t="n"/>
@@ -1218,7 +1194,7 @@
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>207</t>
         </is>
       </c>
       <c r="B23" s="7" t="n"/>
@@ -1237,7 +1213,7 @@
     <row r="24" ht="34" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>208</t>
         </is>
       </c>
       <c r="B24" s="7" t="n"/>
@@ -1256,7 +1232,7 @@
     <row r="25" ht="34" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -1275,7 +1251,7 @@
     <row r="26" ht="34" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B26" s="7" t="n"/>
@@ -1294,7 +1270,7 @@
     <row r="27" ht="34" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>3 A</t>
         </is>
       </c>
       <c r="B27" s="7" t="n"/>
@@ -1313,7 +1289,7 @@
     <row r="28" ht="34" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>3 A</t>
+          <t>3 B</t>
         </is>
       </c>
       <c r="B28" s="7" t="n"/>
@@ -1332,7 +1308,7 @@
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>3 B</t>
+          <t>301</t>
         </is>
       </c>
       <c r="B29" s="7" t="n"/>
@@ -1351,7 +1327,7 @@
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>302</t>
         </is>
       </c>
       <c r="B30" s="7" t="n"/>
@@ -1370,7 +1346,7 @@
     <row r="31" ht="34" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>303</t>
         </is>
       </c>
       <c r="B31" s="7" t="n"/>
@@ -1389,7 +1365,7 @@
     <row r="32" ht="34" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>307</t>
         </is>
       </c>
       <c r="B32" s="7" t="n"/>
@@ -1408,7 +1384,7 @@
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>308</t>
         </is>
       </c>
       <c r="B33" s="7" t="n"/>
@@ -1427,7 +1403,7 @@
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>309</t>
         </is>
       </c>
       <c r="B34" s="7" t="n"/>
@@ -1446,7 +1422,7 @@
     <row r="35" ht="34" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>310</t>
         </is>
       </c>
       <c r="B35" s="7" t="n"/>
@@ -1465,7 +1441,7 @@
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>311</t>
         </is>
       </c>
       <c r="B36" s="7" t="n"/>
@@ -1484,7 +1460,7 @@
     <row r="37" ht="34" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>312</t>
         </is>
       </c>
       <c r="B37" s="7" t="n"/>
@@ -1503,7 +1479,7 @@
     <row r="38" ht="34" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>313</t>
         </is>
       </c>
       <c r="B38" s="7" t="n"/>
@@ -1519,55 +1495,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="34" customHeight="1">
+    <row r="39" ht="40" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>Unused</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="n"/>
-      <c r="E39" s="8" t="n"/>
-      <c r="F39" s="8" t="n"/>
-      <c r="G39" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" ht="40" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B40" s="6" t="n"/>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6" t="n"/>
-      <c r="E40" s="6" t="n"/>
-      <c r="F40" s="6" t="n"/>
-      <c r="G40" s="6" t="n">
-        <v>225</v>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n"/>
+      <c r="G39" s="6" t="n">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="13">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A9:A14"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B13:B14"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="A15:A16"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A40:F40"/>
     <mergeCell ref="A7:G7"/>
-    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -8764,7 +8720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -8847,7 +8803,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="C5" s="12" t="n"/>
       <c r="D5" s="12" t="n"/>
@@ -8864,7 +8820,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="C6" s="12" t="n"/>
       <c r="D6" s="12" t="n"/>
@@ -8881,7 +8837,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="C7" s="12" t="n"/>
       <c r="D7" s="12" t="n"/>
@@ -8898,7 +8854,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>907</v>
+        <v>958</v>
       </c>
       <c r="C8" s="12" t="n"/>
       <c r="D8" s="12" t="n"/>
@@ -8915,7 +8871,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C9" s="12" t="n"/>
       <c r="D9" s="12" t="n"/>
@@ -9012,22 +8968,22 @@
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>1-14,16-22,24-32</t>
+          <t>1-30</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
@@ -9049,22 +9005,22 @@
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>33-62</t>
+          <t>31-60</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
@@ -9084,26 +9040,26 @@
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>63-80</t>
+          <t>61-63</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I15" s="15" t="n"/>
     </row>
@@ -9119,7 +9075,7 @@
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
@@ -9129,16 +9085,16 @@
       </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>1-8,10-13</t>
+          <t>1-27</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I16" s="15" t="n"/>
     </row>
@@ -9154,7 +9110,7 @@
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
@@ -9164,57 +9120,53 @@
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>14-23,25-48</t>
+          <t>28-51</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="I17" s="15" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n">
-        <v>16</v>
-      </c>
-      <c r="C18" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>Computer Science</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>Database Management</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>49-60</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="I18" s="16" t="n">
-        <v>0</v>
-      </c>
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>SYBMS (Finance)</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>Cost Accounting I (Minor)</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>1-10</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" s="15" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
@@ -9222,73 +9174,73 @@
           <t>117</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n"/>
+      <c r="B19" s="16" t="n">
+        <v>16</v>
+      </c>
       <c r="C19" s="16" t="n">
         <v>5</v>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="E19" s="16" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="G19" s="16" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>11-24</t>
         </is>
       </c>
       <c r="H19" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="I19" s="16" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="I19" s="16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="n">
-        <v>53</v>
-      </c>
-      <c r="C20" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
-        </is>
-      </c>
-      <c r="E20" s="15" t="inlineStr">
-        <is>
-          <t>Biotechnology</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="G20" s="15" t="inlineStr">
-        <is>
-          <t>5-11,13-35</t>
-        </is>
-      </c>
-      <c r="H20" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="I20" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>SYBMS (Marketing)</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H20" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="16" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
@@ -9296,531 +9248,482 @@
           <t>201</t>
         </is>
       </c>
-      <c r="B21" s="15" t="n"/>
+      <c r="B21" s="15" t="n">
+        <v>53</v>
+      </c>
       <c r="C21" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>36-40</t>
+          <t>3-4,7-14,19-22,24,28-29,34-35,40-47,49,51-52,56,58-59,61</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="I21" s="15" t="n"/>
+        <v>34</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="G22" s="15" t="inlineStr">
-        <is>
-          <t>1-18</t>
-        </is>
-      </c>
-      <c r="H22" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="I22" s="15" t="n"/>
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="inlineStr"/>
+      <c r="E22" s="16" t="inlineStr"/>
+      <c r="F22" s="16" t="inlineStr"/>
+      <c r="G22" s="16" t="inlineStr"/>
+      <c r="H22" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="16" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="n">
-        <v>65</v>
-      </c>
-      <c r="C23" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>19-50</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="n">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="n">
+        <v>64</v>
+      </c>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="15" t="inlineStr"/>
+      <c r="E23" s="15" t="inlineStr"/>
+      <c r="F23" s="15" t="inlineStr"/>
+      <c r="G23" s="15" t="inlineStr"/>
+      <c r="H23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="inlineStr"/>
+      <c r="E24" s="16" t="inlineStr"/>
+      <c r="F24" s="16" t="inlineStr"/>
+      <c r="G24" s="16" t="inlineStr"/>
+      <c r="H24" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="16" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="n">
+        <v>64</v>
+      </c>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="inlineStr"/>
+      <c r="E25" s="15" t="inlineStr"/>
+      <c r="F25" s="15" t="inlineStr"/>
+      <c r="G25" s="15" t="inlineStr"/>
+      <c r="H25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="16" t="inlineStr"/>
+      <c r="E26" s="16" t="inlineStr"/>
+      <c r="F26" s="16" t="inlineStr"/>
+      <c r="G26" s="16" t="inlineStr"/>
+      <c r="H26" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="16" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n">
+        <v>53</v>
+      </c>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="15" t="inlineStr"/>
+      <c r="E27" s="15" t="inlineStr"/>
+      <c r="F27" s="15" t="inlineStr"/>
+      <c r="G27" s="15" t="inlineStr"/>
+      <c r="H27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="n">
+        <v>34</v>
+      </c>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="inlineStr"/>
+      <c r="E28" s="16" t="inlineStr"/>
+      <c r="F28" s="16" t="inlineStr"/>
+      <c r="G28" s="16" t="inlineStr"/>
+      <c r="H28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="16" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="15" t="inlineStr"/>
+      <c r="E29" s="15" t="inlineStr"/>
+      <c r="F29" s="15" t="inlineStr"/>
+      <c r="G29" s="15" t="inlineStr"/>
+      <c r="H29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16" t="inlineStr"/>
+      <c r="E30" s="16" t="inlineStr"/>
+      <c r="F30" s="16" t="inlineStr"/>
+      <c r="G30" s="16" t="inlineStr"/>
+      <c r="H30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="16" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>3 A</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="15" t="inlineStr"/>
+      <c r="E31" s="15" t="inlineStr"/>
+      <c r="F31" s="15" t="inlineStr"/>
+      <c r="G31" s="15" t="inlineStr"/>
+      <c r="H31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>3 B</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="n">
+        <v>37</v>
+      </c>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="inlineStr"/>
+      <c r="E32" s="16" t="inlineStr"/>
+      <c r="F32" s="16" t="inlineStr"/>
+      <c r="G32" s="16" t="inlineStr"/>
+      <c r="H32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="16" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="15" t="inlineStr"/>
+      <c r="E33" s="15" t="inlineStr"/>
+      <c r="F33" s="15" t="inlineStr"/>
+      <c r="G33" s="15" t="inlineStr"/>
+      <c r="H33" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="n">
+        <v>56</v>
+      </c>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="16" t="inlineStr"/>
+      <c r="E34" s="16" t="inlineStr"/>
+      <c r="F34" s="16" t="inlineStr"/>
+      <c r="G34" s="16" t="inlineStr"/>
+      <c r="H34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="16" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="n">
+        <v>56</v>
+      </c>
+      <c r="C35" s="15" t="n"/>
+      <c r="D35" s="15" t="inlineStr"/>
+      <c r="E35" s="15" t="inlineStr"/>
+      <c r="F35" s="15" t="inlineStr"/>
+      <c r="G35" s="15" t="inlineStr"/>
+      <c r="H35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="15" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="n">
+        <v>57</v>
+      </c>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="16" t="inlineStr"/>
+      <c r="E36" s="16" t="inlineStr"/>
+      <c r="F36" s="16" t="inlineStr"/>
+      <c r="G36" s="16" t="inlineStr"/>
+      <c r="H36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="16" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="n">
+        <v>66</v>
+      </c>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="15" t="inlineStr"/>
+      <c r="E37" s="15" t="inlineStr"/>
+      <c r="F37" s="15" t="inlineStr"/>
+      <c r="G37" s="15" t="inlineStr"/>
+      <c r="H37" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="15" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="n">
         <v>32</v>
       </c>
-      <c r="I23" s="16" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="n">
-        <v>64</v>
-      </c>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="15" t="inlineStr"/>
-      <c r="E24" s="15" t="inlineStr"/>
-      <c r="F24" s="15" t="inlineStr"/>
-      <c r="G24" s="15" t="inlineStr"/>
-      <c r="H24" s="15" t="n">
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="16" t="inlineStr"/>
+      <c r="E38" s="16" t="inlineStr"/>
+      <c r="F38" s="16" t="inlineStr"/>
+      <c r="G38" s="16" t="inlineStr"/>
+      <c r="H38" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="15" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="n">
+      <c r="I38" s="16" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="inlineStr"/>
-      <c r="E25" s="16" t="inlineStr"/>
-      <c r="F25" s="16" t="inlineStr"/>
-      <c r="G25" s="16" t="inlineStr"/>
-      <c r="H25" s="16" t="n">
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="inlineStr"/>
+      <c r="E39" s="15" t="inlineStr"/>
+      <c r="F39" s="15" t="inlineStr"/>
+      <c r="G39" s="15" t="inlineStr"/>
+      <c r="H39" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="I25" s="16" t="n">
+      <c r="I39" s="15" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="n">
-        <v>64</v>
-      </c>
-      <c r="C26" s="15" t="n"/>
-      <c r="D26" s="15" t="inlineStr"/>
-      <c r="E26" s="15" t="inlineStr"/>
-      <c r="F26" s="15" t="inlineStr"/>
-      <c r="G26" s="15" t="inlineStr"/>
-      <c r="H26" s="15" t="n">
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="B40" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="16" t="inlineStr"/>
+      <c r="E40" s="16" t="inlineStr"/>
+      <c r="F40" s="16" t="inlineStr"/>
+      <c r="G40" s="16" t="inlineStr"/>
+      <c r="H40" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="15" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n">
-        <v>61</v>
-      </c>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="inlineStr"/>
-      <c r="E27" s="16" t="inlineStr"/>
-      <c r="F27" s="16" t="inlineStr"/>
-      <c r="G27" s="16" t="inlineStr"/>
-      <c r="H27" s="16" t="n">
+      <c r="I40" s="16" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="15" t="inlineStr"/>
+      <c r="E41" s="15" t="inlineStr"/>
+      <c r="F41" s="15" t="inlineStr"/>
+      <c r="G41" s="15" t="inlineStr"/>
+      <c r="H41" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="16" t="n">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="n">
-        <v>53</v>
-      </c>
-      <c r="C28" s="15" t="n"/>
-      <c r="D28" s="15" t="inlineStr"/>
-      <c r="E28" s="15" t="inlineStr"/>
-      <c r="F28" s="15" t="inlineStr"/>
-      <c r="G28" s="15" t="inlineStr"/>
-      <c r="H28" s="15" t="n">
+      <c r="I41" s="15" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="n">
+        <v>66</v>
+      </c>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="16" t="inlineStr"/>
+      <c r="E42" s="16" t="inlineStr"/>
+      <c r="F42" s="16" t="inlineStr"/>
+      <c r="G42" s="16" t="inlineStr"/>
+      <c r="H42" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="15" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="n">
-        <v>34</v>
-      </c>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="inlineStr"/>
-      <c r="E29" s="16" t="inlineStr"/>
-      <c r="F29" s="16" t="inlineStr"/>
-      <c r="G29" s="16" t="inlineStr"/>
-      <c r="H29" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="16" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="C30" s="15" t="n"/>
-      <c r="D30" s="15" t="inlineStr"/>
-      <c r="E30" s="15" t="inlineStr"/>
-      <c r="F30" s="15" t="inlineStr"/>
-      <c r="G30" s="15" t="inlineStr"/>
-      <c r="H30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="15" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="n">
-        <v>26</v>
-      </c>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="inlineStr"/>
-      <c r="E31" s="16" t="inlineStr"/>
-      <c r="F31" s="16" t="inlineStr"/>
-      <c r="G31" s="16" t="inlineStr"/>
-      <c r="H31" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="16" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>3 A</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="n">
-        <v>38</v>
-      </c>
-      <c r="C32" s="15" t="n"/>
-      <c r="D32" s="15" t="inlineStr"/>
-      <c r="E32" s="15" t="inlineStr"/>
-      <c r="F32" s="15" t="inlineStr"/>
-      <c r="G32" s="15" t="inlineStr"/>
-      <c r="H32" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="15" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>3 B</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="n">
-        <v>37</v>
-      </c>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="inlineStr"/>
-      <c r="E33" s="16" t="inlineStr"/>
-      <c r="F33" s="16" t="inlineStr"/>
-      <c r="G33" s="16" t="inlineStr"/>
-      <c r="H33" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="16" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="C34" s="15" t="n"/>
-      <c r="D34" s="15" t="inlineStr"/>
-      <c r="E34" s="15" t="inlineStr"/>
-      <c r="F34" s="15" t="inlineStr"/>
-      <c r="G34" s="15" t="inlineStr"/>
-      <c r="H34" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="15" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="n">
-        <v>56</v>
-      </c>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="inlineStr"/>
-      <c r="E35" s="16" t="inlineStr"/>
-      <c r="F35" s="16" t="inlineStr"/>
-      <c r="G35" s="16" t="inlineStr"/>
-      <c r="H35" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="16" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="n">
-        <v>56</v>
-      </c>
-      <c r="C36" s="15" t="n"/>
-      <c r="D36" s="15" t="inlineStr"/>
-      <c r="E36" s="15" t="inlineStr"/>
-      <c r="F36" s="15" t="inlineStr"/>
-      <c r="G36" s="15" t="inlineStr"/>
-      <c r="H36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="15" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="n">
-        <v>57</v>
-      </c>
-      <c r="C37" s="16" t="n"/>
-      <c r="D37" s="16" t="inlineStr"/>
-      <c r="E37" s="16" t="inlineStr"/>
-      <c r="F37" s="16" t="inlineStr"/>
-      <c r="G37" s="16" t="inlineStr"/>
-      <c r="H37" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="16" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="n">
+      <c r="I42" s="16" t="n">
         <v>66</v>
       </c>
-      <c r="C38" s="15" t="n"/>
-      <c r="D38" s="15" t="inlineStr"/>
-      <c r="E38" s="15" t="inlineStr"/>
-      <c r="F38" s="15" t="inlineStr"/>
-      <c r="G38" s="15" t="inlineStr"/>
-      <c r="H38" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="15" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="n">
-        <v>32</v>
-      </c>
-      <c r="C39" s="16" t="n"/>
-      <c r="D39" s="16" t="inlineStr"/>
-      <c r="E39" s="16" t="inlineStr"/>
-      <c r="F39" s="16" t="inlineStr"/>
-      <c r="G39" s="16" t="inlineStr"/>
-      <c r="H39" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="16" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="n">
-        <v>22</v>
-      </c>
-      <c r="C40" s="15" t="n"/>
-      <c r="D40" s="15" t="inlineStr"/>
-      <c r="E40" s="15" t="inlineStr"/>
-      <c r="F40" s="15" t="inlineStr"/>
-      <c r="G40" s="15" t="inlineStr"/>
-      <c r="H40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="15" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="16" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="inlineStr"/>
-      <c r="E41" s="16" t="inlineStr"/>
-      <c r="F41" s="16" t="inlineStr"/>
-      <c r="G41" s="16" t="inlineStr"/>
-      <c r="H41" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="16" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="B42" s="15" t="n">
-        <v>60</v>
-      </c>
-      <c r="C42" s="15" t="n"/>
-      <c r="D42" s="15" t="inlineStr"/>
-      <c r="E42" s="15" t="inlineStr"/>
-      <c r="F42" s="15" t="inlineStr"/>
-      <c r="G42" s="15" t="inlineStr"/>
-      <c r="H42" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="15" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="n">
-        <v>66</v>
-      </c>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="inlineStr"/>
-      <c r="E43" s="16" t="inlineStr"/>
-      <c r="F43" s="16" t="inlineStr"/>
-      <c r="G43" s="16" t="inlineStr"/>
-      <c r="H43" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="16" t="n">
-        <v>66</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A12:I43"/>
+  <autoFilter ref="A12:I42"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A10:I10"/>
@@ -16415,7 +16318,7 @@
         </is>
       </c>
       <c r="B2" s="18" t="n">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="C2" s="12" t="n"/>
       <c r="D2" s="12" t="n"/>
@@ -16433,7 +16336,7 @@
         </is>
       </c>
       <c r="B3" s="18" t="n">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="C3" s="12" t="n"/>
       <c r="D3" s="12" t="n"/>
@@ -16451,7 +16354,7 @@
         </is>
       </c>
       <c r="B4" s="18" t="n">
-        <v>225</v>
+        <v>174</v>
       </c>
       <c r="C4" s="12" t="n"/>
       <c r="D4" s="12" t="n"/>
@@ -16469,7 +16372,7 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>907</v>
+        <v>958</v>
       </c>
       <c r="C5" s="12" t="n"/>
       <c r="D5" s="12" t="n"/>
@@ -16580,21 +16483,21 @@
       </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
         <is>
-          <t>1-14,16-22,24-80</t>
+          <t>1-63</t>
         </is>
       </c>
       <c r="I9" s="22" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="J9" s="22" t="n">
         <v>0</v>
@@ -16618,21 +16521,21 @@
       <c r="E10" s="22" t="n"/>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
         <is>
-          <t>1-8,10-23,25-48</t>
+          <t>1-51</t>
         </is>
       </c>
       <c r="I10" s="22" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J10" s="22" t="n"/>
     </row>
@@ -16648,33 +16551,29 @@
       </c>
       <c r="D11" s="22" t="inlineStr">
         <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="n">
-        <v>16</v>
-      </c>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="n"/>
       <c r="F11" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
         <is>
-          <t>49-60</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="I11" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="J11" s="22" t="n">
-        <v>0</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="J11" s="22" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="20" t="n">
@@ -16691,26 +16590,30 @@
           <t>117</t>
         </is>
       </c>
-      <c r="E12" s="22" t="n"/>
+      <c r="E12" s="22" t="n">
+        <v>16</v>
+      </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>11-24</t>
         </is>
       </c>
       <c r="I12" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="J12" s="22" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="J12" s="22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="20" t="n">
@@ -16724,33 +16627,29 @@
       </c>
       <c r="D13" s="22" t="inlineStr">
         <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="n">
-        <v>53</v>
-      </c>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="n"/>
       <c r="F13" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
         <is>
-          <t>5-11,13-40</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I13" s="22" t="n">
-        <v>35</v>
-      </c>
-      <c r="J13" s="22" t="n">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J13" s="22" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="20" t="n">
@@ -16767,26 +16666,30 @@
           <t>201</t>
         </is>
       </c>
-      <c r="E14" s="22" t="n"/>
+      <c r="E14" s="22" t="n">
+        <v>53</v>
+      </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
         <is>
-          <t>1-18</t>
+          <t>3-4,7-14,19-22,24,28-29,34-35,40-47,49,51-52,56,58-59,61</t>
         </is>
       </c>
       <c r="I14" s="22" t="n">
-        <v>18</v>
-      </c>
-      <c r="J14" s="22" t="n"/>
+        <v>34</v>
+      </c>
+      <c r="J14" s="22" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="20" t="n">
@@ -16806,26 +16709,14 @@
       <c r="E15" s="22" t="n">
         <v>65</v>
       </c>
-      <c r="F15" s="22" t="inlineStr">
-        <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="G15" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="H15" s="22" t="inlineStr">
-        <is>
-          <t>19-50</t>
-        </is>
-      </c>
+      <c r="F15" s="22" t="inlineStr"/>
+      <c r="G15" s="22" t="inlineStr"/>
+      <c r="H15" s="22" t="inlineStr"/>
       <c r="I15" s="22" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J15" s="22" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
@@ -17546,17 +17437,17 @@
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F8" s="22" t="n">
@@ -17572,17 +17463,17 @@
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F9" s="22" t="n">
@@ -17598,17 +17489,17 @@
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F10" s="22" t="n">
@@ -17624,17 +17515,17 @@
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F11" s="22" t="n">
@@ -17650,17 +17541,17 @@
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F12" s="22" t="n">
@@ -17676,17 +17567,17 @@
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F13" s="22" t="n">
@@ -17702,17 +17593,17 @@
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F14" s="22" t="n">
@@ -17728,17 +17619,17 @@
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F15" s="22" t="n">
@@ -17754,17 +17645,17 @@
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F16" s="22" t="n">
@@ -17780,17 +17671,17 @@
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F17" s="22" t="n">
@@ -17806,17 +17697,17 @@
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F18" s="22" t="n">
@@ -17832,17 +17723,17 @@
       </c>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F19" s="22" t="n">
@@ -17858,17 +17749,17 @@
       </c>
       <c r="C20" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F20" s="22" t="n">
@@ -17884,17 +17775,17 @@
       </c>
       <c r="C21" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F21" s="22" t="n">
@@ -17910,21 +17801,21 @@
       </c>
       <c r="C22" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F22" s="22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
@@ -17936,21 +17827,21 @@
       </c>
       <c r="C23" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F23" s="22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
@@ -17962,21 +17853,21 @@
       </c>
       <c r="C24" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F24" s="22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
@@ -17988,21 +17879,21 @@
       </c>
       <c r="C25" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F25" s="22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
@@ -18014,21 +17905,21 @@
       </c>
       <c r="C26" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F26" s="22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
@@ -18040,21 +17931,21 @@
       </c>
       <c r="C27" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F27" s="22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
@@ -18066,21 +17957,21 @@
       </c>
       <c r="C28" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F28" s="22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
@@ -18092,21 +17983,21 @@
       </c>
       <c r="C29" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F29" s="22" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
@@ -18118,21 +18009,21 @@
       </c>
       <c r="C30" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F30" s="22" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
@@ -18144,21 +18035,21 @@
       </c>
       <c r="C31" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F31" s="22" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
@@ -18170,21 +18061,21 @@
       </c>
       <c r="C32" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F32" s="22" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
@@ -18196,21 +18087,21 @@
       </c>
       <c r="C33" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F33" s="22" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
@@ -18222,21 +18113,21 @@
       </c>
       <c r="C34" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F34" s="22" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
@@ -18248,21 +18139,21 @@
       </c>
       <c r="C35" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F35" s="22" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
@@ -18274,21 +18165,21 @@
       </c>
       <c r="C36" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F36" s="22" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
@@ -18300,21 +18191,21 @@
       </c>
       <c r="C37" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F37" s="22" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
@@ -18326,21 +18217,21 @@
       </c>
       <c r="C38" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D38" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E38" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F38" s="22" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
@@ -18352,21 +18243,21 @@
       </c>
       <c r="C39" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D39" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E39" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F39" s="22" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
@@ -18378,21 +18269,21 @@
       </c>
       <c r="C40" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D40" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E40" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F40" s="22" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
@@ -18404,21 +18295,21 @@
       </c>
       <c r="C41" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D41" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E41" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F41" s="22" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
@@ -18430,21 +18321,21 @@
       </c>
       <c r="C42" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D42" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E42" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F42" s="22" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
@@ -18456,21 +18347,21 @@
       </c>
       <c r="C43" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D43" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E43" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F43" s="22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
@@ -18482,21 +18373,21 @@
       </c>
       <c r="C44" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D44" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E44" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F44" s="22" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
@@ -18508,21 +18399,21 @@
       </c>
       <c r="C45" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D45" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E45" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F45" s="22" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
@@ -18534,21 +18425,21 @@
       </c>
       <c r="C46" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D46" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E46" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F46" s="22" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
@@ -18560,21 +18451,21 @@
       </c>
       <c r="C47" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D47" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E47" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F47" s="22" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
@@ -18586,21 +18477,21 @@
       </c>
       <c r="C48" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D48" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E48" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F48" s="22" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
@@ -18612,21 +18503,21 @@
       </c>
       <c r="C49" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D49" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E49" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F49" s="22" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
@@ -18638,21 +18529,21 @@
       </c>
       <c r="C50" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D50" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E50" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F50" s="22" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
@@ -18664,21 +18555,21 @@
       </c>
       <c r="C51" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D51" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E51" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F51" s="22" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
@@ -18690,21 +18581,21 @@
       </c>
       <c r="C52" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D52" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E52" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F52" s="22" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
@@ -18716,21 +18607,21 @@
       </c>
       <c r="C53" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D53" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E53" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F53" s="22" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
@@ -18742,21 +18633,21 @@
       </c>
       <c r="C54" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D54" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E54" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F54" s="22" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
@@ -18768,21 +18659,21 @@
       </c>
       <c r="C55" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D55" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E55" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F55" s="22" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
@@ -18794,21 +18685,21 @@
       </c>
       <c r="C56" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D56" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E56" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F56" s="22" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
@@ -18820,21 +18711,21 @@
       </c>
       <c r="C57" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D57" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E57" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F57" s="22" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
@@ -18846,21 +18737,21 @@
       </c>
       <c r="C58" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D58" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E58" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F58" s="22" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
@@ -18872,21 +18763,21 @@
       </c>
       <c r="C59" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D59" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E59" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F59" s="22" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
@@ -18898,21 +18789,21 @@
       </c>
       <c r="C60" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D60" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E60" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F60" s="22" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
@@ -18924,21 +18815,21 @@
       </c>
       <c r="C61" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D61" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E61" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F61" s="22" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
@@ -18950,21 +18841,21 @@
       </c>
       <c r="C62" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D62" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E62" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F62" s="22" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
@@ -18976,21 +18867,21 @@
       </c>
       <c r="C63" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D63" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E63" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F63" s="22" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
@@ -19002,21 +18893,21 @@
       </c>
       <c r="C64" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D64" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E64" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F64" s="22" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
@@ -19028,21 +18919,21 @@
       </c>
       <c r="C65" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D65" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E65" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F65" s="22" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
@@ -19054,21 +18945,21 @@
       </c>
       <c r="C66" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D66" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E66" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F66" s="22" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="67" ht="30" customHeight="1">
@@ -19080,21 +18971,21 @@
       </c>
       <c r="C67" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D67" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E67" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F67" s="22" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
@@ -19106,21 +18997,21 @@
       </c>
       <c r="C68" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D68" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E68" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F68" s="22" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
@@ -19132,21 +19023,21 @@
       </c>
       <c r="C69" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D69" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E69" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F69" s="22" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
@@ -19158,21 +19049,21 @@
       </c>
       <c r="C70" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>FYCS</t>
         </is>
       </c>
       <c r="D70" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E70" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>DBMS (Major)</t>
         </is>
       </c>
       <c r="F70" s="22" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
@@ -19184,21 +19075,21 @@
       </c>
       <c r="C71" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D71" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E71" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F71" s="22" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" ht="30" customHeight="1">
@@ -19210,21 +19101,21 @@
       </c>
       <c r="C72" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D72" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E72" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F72" s="22" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" ht="30" customHeight="1">
@@ -19236,21 +19127,21 @@
       </c>
       <c r="C73" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D73" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E73" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F73" s="22" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" ht="30" customHeight="1">
@@ -19262,21 +19153,21 @@
       </c>
       <c r="C74" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D74" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E74" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F74" s="22" t="n">
-        <v>69</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75" ht="30" customHeight="1">
@@ -19288,21 +19179,21 @@
       </c>
       <c r="C75" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D75" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E75" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F75" s="22" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" ht="30" customHeight="1">
@@ -19314,21 +19205,21 @@
       </c>
       <c r="C76" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D76" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E76" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F76" s="22" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" ht="30" customHeight="1">
@@ -19340,21 +19231,21 @@
       </c>
       <c r="C77" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D77" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E77" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F77" s="22" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" ht="30" customHeight="1">
@@ -19366,21 +19257,21 @@
       </c>
       <c r="C78" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D78" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E78" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F78" s="22" t="n">
-        <v>73</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79" ht="30" customHeight="1">
@@ -19392,21 +19283,21 @@
       </c>
       <c r="C79" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D79" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E79" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F79" s="22" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" ht="30" customHeight="1">
@@ -19418,21 +19309,21 @@
       </c>
       <c r="C80" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D80" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E80" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F80" s="22" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81" ht="30" customHeight="1">
@@ -19444,21 +19335,21 @@
       </c>
       <c r="C81" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D81" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E81" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F81" s="22" t="n">
-        <v>76</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82" ht="30" customHeight="1">
@@ -19470,21 +19361,21 @@
       </c>
       <c r="C82" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D82" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E82" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F82" s="22" t="n">
-        <v>77</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" ht="30" customHeight="1">
@@ -19496,21 +19387,21 @@
       </c>
       <c r="C83" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D83" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E83" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F83" s="22" t="n">
-        <v>78</v>
+        <v>13</v>
       </c>
     </row>
     <row r="84" ht="30" customHeight="1">
@@ -19522,21 +19413,21 @@
       </c>
       <c r="C84" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D84" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E84" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F84" s="22" t="n">
-        <v>79</v>
+        <v>14</v>
       </c>
     </row>
     <row r="85" ht="30" customHeight="1">
@@ -19548,21 +19439,21 @@
       </c>
       <c r="C85" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Com</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D85" s="22" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="E85" s="22" t="inlineStr">
         <is>
-          <t>Cost Accounting</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F85" s="22" t="n">
-        <v>80</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86" ht="30" customHeight="1">
@@ -19574,7 +19465,7 @@
       </c>
       <c r="C86" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D86" s="22" t="inlineStr">
@@ -19584,11 +19475,11 @@
       </c>
       <c r="E86" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F86" s="22" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87" ht="30" customHeight="1">
@@ -19600,7 +19491,7 @@
       </c>
       <c r="C87" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D87" s="22" t="inlineStr">
@@ -19610,11 +19501,11 @@
       </c>
       <c r="E87" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F87" s="22" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="88" ht="30" customHeight="1">
@@ -19626,7 +19517,7 @@
       </c>
       <c r="C88" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D88" s="22" t="inlineStr">
@@ -19636,11 +19527,11 @@
       </c>
       <c r="E88" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F88" s="22" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89" ht="30" customHeight="1">
@@ -19652,7 +19543,7 @@
       </c>
       <c r="C89" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D89" s="22" t="inlineStr">
@@ -19662,11 +19553,11 @@
       </c>
       <c r="E89" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F89" s="22" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" ht="30" customHeight="1">
@@ -19678,7 +19569,7 @@
       </c>
       <c r="C90" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D90" s="22" t="inlineStr">
@@ -19688,11 +19579,11 @@
       </c>
       <c r="E90" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F90" s="22" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" ht="30" customHeight="1">
@@ -19704,7 +19595,7 @@
       </c>
       <c r="C91" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D91" s="22" t="inlineStr">
@@ -19714,11 +19605,11 @@
       </c>
       <c r="E91" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F91" s="22" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="92" ht="30" customHeight="1">
@@ -19730,7 +19621,7 @@
       </c>
       <c r="C92" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D92" s="22" t="inlineStr">
@@ -19740,11 +19631,11 @@
       </c>
       <c r="E92" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F92" s="22" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93" ht="30" customHeight="1">
@@ -19756,7 +19647,7 @@
       </c>
       <c r="C93" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D93" s="22" t="inlineStr">
@@ -19766,11 +19657,11 @@
       </c>
       <c r="E93" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F93" s="22" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94" ht="30" customHeight="1">
@@ -19782,7 +19673,7 @@
       </c>
       <c r="C94" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D94" s="22" t="inlineStr">
@@ -19792,11 +19683,11 @@
       </c>
       <c r="E94" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F94" s="22" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95" ht="30" customHeight="1">
@@ -19808,7 +19699,7 @@
       </c>
       <c r="C95" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D95" s="22" t="inlineStr">
@@ -19818,11 +19709,11 @@
       </c>
       <c r="E95" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F95" s="22" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96" ht="30" customHeight="1">
@@ -19834,7 +19725,7 @@
       </c>
       <c r="C96" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D96" s="22" t="inlineStr">
@@ -19844,11 +19735,11 @@
       </c>
       <c r="E96" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F96" s="22" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97" ht="30" customHeight="1">
@@ -19860,7 +19751,7 @@
       </c>
       <c r="C97" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D97" s="22" t="inlineStr">
@@ -19870,11 +19761,11 @@
       </c>
       <c r="E97" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F97" s="22" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="98" ht="30" customHeight="1">
@@ -19886,7 +19777,7 @@
       </c>
       <c r="C98" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D98" s="22" t="inlineStr">
@@ -19896,11 +19787,11 @@
       </c>
       <c r="E98" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F98" s="22" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="99" ht="30" customHeight="1">
@@ -19912,7 +19803,7 @@
       </c>
       <c r="C99" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D99" s="22" t="inlineStr">
@@ -19922,11 +19813,11 @@
       </c>
       <c r="E99" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F99" s="22" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="100" ht="30" customHeight="1">
@@ -19938,7 +19829,7 @@
       </c>
       <c r="C100" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D100" s="22" t="inlineStr">
@@ -19948,11 +19839,11 @@
       </c>
       <c r="E100" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F100" s="22" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="101" ht="30" customHeight="1">
@@ -19964,7 +19855,7 @@
       </c>
       <c r="C101" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D101" s="22" t="inlineStr">
@@ -19974,11 +19865,11 @@
       </c>
       <c r="E101" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F101" s="22" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="102" ht="30" customHeight="1">
@@ -19990,7 +19881,7 @@
       </c>
       <c r="C102" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D102" s="22" t="inlineStr">
@@ -20000,11 +19891,11 @@
       </c>
       <c r="E102" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F102" s="22" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="103" ht="30" customHeight="1">
@@ -20016,7 +19907,7 @@
       </c>
       <c r="C103" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D103" s="22" t="inlineStr">
@@ -20026,11 +19917,11 @@
       </c>
       <c r="E103" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F103" s="22" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="104" ht="30" customHeight="1">
@@ -20042,7 +19933,7 @@
       </c>
       <c r="C104" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D104" s="22" t="inlineStr">
@@ -20052,11 +19943,11 @@
       </c>
       <c r="E104" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F104" s="22" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="105" ht="30" customHeight="1">
@@ -20068,7 +19959,7 @@
       </c>
       <c r="C105" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D105" s="22" t="inlineStr">
@@ -20078,11 +19969,11 @@
       </c>
       <c r="E105" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F105" s="22" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="106" ht="30" customHeight="1">
@@ -20094,7 +19985,7 @@
       </c>
       <c r="C106" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D106" s="22" t="inlineStr">
@@ -20104,11 +19995,11 @@
       </c>
       <c r="E106" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F106" s="22" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="107" ht="30" customHeight="1">
@@ -20120,7 +20011,7 @@
       </c>
       <c r="C107" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D107" s="22" t="inlineStr">
@@ -20130,11 +20021,11 @@
       </c>
       <c r="E107" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F107" s="22" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="108" ht="30" customHeight="1">
@@ -20146,7 +20037,7 @@
       </c>
       <c r="C108" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D108" s="22" t="inlineStr">
@@ -20156,11 +20047,11 @@
       </c>
       <c r="E108" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F108" s="22" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="109" ht="30" customHeight="1">
@@ -20172,7 +20063,7 @@
       </c>
       <c r="C109" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D109" s="22" t="inlineStr">
@@ -20182,11 +20073,11 @@
       </c>
       <c r="E109" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F109" s="22" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="110" ht="30" customHeight="1">
@@ -20198,7 +20089,7 @@
       </c>
       <c r="C110" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D110" s="22" t="inlineStr">
@@ -20208,11 +20099,11 @@
       </c>
       <c r="E110" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F110" s="22" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="111" ht="30" customHeight="1">
@@ -20224,7 +20115,7 @@
       </c>
       <c r="C111" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D111" s="22" t="inlineStr">
@@ -20234,11 +20125,11 @@
       </c>
       <c r="E111" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F111" s="22" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
     </row>
     <row r="112" ht="30" customHeight="1">
@@ -20250,7 +20141,7 @@
       </c>
       <c r="C112" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D112" s="22" t="inlineStr">
@@ -20260,11 +20151,11 @@
       </c>
       <c r="E112" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F112" s="22" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="113" ht="30" customHeight="1">
@@ -20276,7 +20167,7 @@
       </c>
       <c r="C113" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D113" s="22" t="inlineStr">
@@ -20286,11 +20177,11 @@
       </c>
       <c r="E113" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F113" s="22" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="114" ht="30" customHeight="1">
@@ -20302,7 +20193,7 @@
       </c>
       <c r="C114" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D114" s="22" t="inlineStr">
@@ -20312,11 +20203,11 @@
       </c>
       <c r="E114" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F114" s="22" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="115" ht="30" customHeight="1">
@@ -20328,7 +20219,7 @@
       </c>
       <c r="C115" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D115" s="22" t="inlineStr">
@@ -20338,11 +20229,11 @@
       </c>
       <c r="E115" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F115" s="22" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="116" ht="30" customHeight="1">
@@ -20354,7 +20245,7 @@
       </c>
       <c r="C116" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D116" s="22" t="inlineStr">
@@ -20364,11 +20255,11 @@
       </c>
       <c r="E116" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F116" s="22" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="117" ht="30" customHeight="1">
@@ -20380,7 +20271,7 @@
       </c>
       <c r="C117" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D117" s="22" t="inlineStr">
@@ -20390,11 +20281,11 @@
       </c>
       <c r="E117" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F117" s="22" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="118" ht="30" customHeight="1">
@@ -20406,7 +20297,7 @@
       </c>
       <c r="C118" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D118" s="22" t="inlineStr">
@@ -20416,11 +20307,11 @@
       </c>
       <c r="E118" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F118" s="22" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="119" ht="30" customHeight="1">
@@ -20432,7 +20323,7 @@
       </c>
       <c r="C119" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D119" s="22" t="inlineStr">
@@ -20442,11 +20333,11 @@
       </c>
       <c r="E119" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F119" s="22" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="120" ht="30" customHeight="1">
@@ -20458,7 +20349,7 @@
       </c>
       <c r="C120" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D120" s="22" t="inlineStr">
@@ -20468,11 +20359,11 @@
       </c>
       <c r="E120" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F120" s="22" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
     </row>
     <row r="121" ht="30" customHeight="1">
@@ -20484,7 +20375,7 @@
       </c>
       <c r="C121" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>TYCS</t>
         </is>
       </c>
       <c r="D121" s="22" t="inlineStr">
@@ -20494,11 +20385,11 @@
       </c>
       <c r="E121" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>IKS (Major)</t>
         </is>
       </c>
       <c r="F121" s="22" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
     </row>
     <row r="122" ht="30" customHeight="1">
@@ -20510,21 +20401,21 @@
       </c>
       <c r="C122" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D122" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E122" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F122" s="22" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" ht="30" customHeight="1">
@@ -20536,21 +20427,21 @@
       </c>
       <c r="C123" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D123" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E123" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F123" s="22" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124" ht="30" customHeight="1">
@@ -20562,21 +20453,21 @@
       </c>
       <c r="C124" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D124" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E124" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F124" s="22" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125" ht="30" customHeight="1">
@@ -20588,21 +20479,21 @@
       </c>
       <c r="C125" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D125" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E125" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F125" s="22" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126" ht="30" customHeight="1">
@@ -20614,21 +20505,21 @@
       </c>
       <c r="C126" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D126" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E126" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F126" s="22" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" ht="30" customHeight="1">
@@ -20640,21 +20531,21 @@
       </c>
       <c r="C127" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D127" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E127" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F127" s="22" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
     </row>
     <row r="128" ht="30" customHeight="1">
@@ -20666,21 +20557,21 @@
       </c>
       <c r="C128" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D128" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E128" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F128" s="22" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
     </row>
     <row r="129" ht="30" customHeight="1">
@@ -20692,21 +20583,21 @@
       </c>
       <c r="C129" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D129" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E129" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F129" s="22" t="n">
-        <v>46</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130" ht="30" customHeight="1">
@@ -20718,21 +20609,21 @@
       </c>
       <c r="C130" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D130" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E130" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F130" s="22" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131" ht="30" customHeight="1">
@@ -20744,21 +20635,21 @@
       </c>
       <c r="C131" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D131" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E131" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F131" s="22" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -20919,21 +20810,21 @@
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F8" s="22" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -20945,21 +20836,21 @@
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F9" s="22" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
@@ -20971,21 +20862,21 @@
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F10" s="22" t="n">
-        <v>51</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
@@ -20997,21 +20888,21 @@
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F11" s="22" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
@@ -21023,21 +20914,21 @@
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F12" s="22" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
@@ -21049,21 +20940,21 @@
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F13" s="22" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
@@ -21075,21 +20966,21 @@
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
@@ -21101,21 +20992,21 @@
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F15" s="22" t="n">
-        <v>56</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
@@ -21127,21 +21018,21 @@
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F16" s="22" t="n">
-        <v>57</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
@@ -21153,21 +21044,21 @@
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F17" s="22" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
@@ -21179,21 +21070,21 @@
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F18" s="22" t="n">
-        <v>59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
@@ -21205,21 +21096,21 @@
       </c>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Computer Science)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>Database Management</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F19" s="22" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
@@ -21231,21 +21122,21 @@
       </c>
       <c r="C20" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F20" s="22" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -21257,21 +21148,21 @@
       </c>
       <c r="C21" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Finance)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Cost Accounting I (Minor)</t>
         </is>
       </c>
       <c r="F21" s="22" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
@@ -21283,21 +21174,21 @@
       </c>
       <c r="C22" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F22" s="22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
@@ -21309,21 +21200,21 @@
       </c>
       <c r="C23" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F23" s="22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -21412,7 +21303,7 @@
         </is>
       </c>
       <c r="D4" s="12" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
@@ -21420,7 +21311,7 @@
         </is>
       </c>
       <c r="F4" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
@@ -21484,21 +21375,21 @@
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F8" s="22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -21510,21 +21401,21 @@
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F9" s="22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
@@ -21536,17 +21427,17 @@
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F10" s="22" t="n">
@@ -21562,17 +21453,17 @@
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F11" s="22" t="n">
@@ -21588,17 +21479,17 @@
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F12" s="22" t="n">
@@ -21614,17 +21505,17 @@
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F13" s="22" t="n">
@@ -21640,17 +21531,17 @@
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F14" s="22" t="n">
@@ -21666,21 +21557,21 @@
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F15" s="22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
@@ -21692,21 +21583,21 @@
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F16" s="22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
@@ -21718,21 +21609,21 @@
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F17" s="22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
@@ -21744,21 +21635,21 @@
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F18" s="22" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
@@ -21770,21 +21661,21 @@
       </c>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F19" s="22" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
@@ -21796,21 +21687,21 @@
       </c>
       <c r="C20" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F20" s="22" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -21822,21 +21713,21 @@
       </c>
       <c r="C21" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F21" s="22" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
@@ -21848,21 +21739,21 @@
       </c>
       <c r="C22" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F22" s="22" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
@@ -21874,21 +21765,21 @@
       </c>
       <c r="C23" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F23" s="22" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
@@ -21900,21 +21791,21 @@
       </c>
       <c r="C24" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F24" s="22" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
@@ -21926,21 +21817,21 @@
       </c>
       <c r="C25" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F25" s="22" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
@@ -21952,21 +21843,21 @@
       </c>
       <c r="C26" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F26" s="22" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
@@ -21978,21 +21869,21 @@
       </c>
       <c r="C27" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F27" s="22" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
@@ -22004,21 +21895,21 @@
       </c>
       <c r="C28" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F28" s="22" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
@@ -22030,21 +21921,21 @@
       </c>
       <c r="C29" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F29" s="22" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
@@ -22056,21 +21947,21 @@
       </c>
       <c r="C30" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F30" s="22" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
@@ -22082,21 +21973,21 @@
       </c>
       <c r="C31" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F31" s="22" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
@@ -22108,21 +21999,21 @@
       </c>
       <c r="C32" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F32" s="22" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
@@ -22134,21 +22025,21 @@
       </c>
       <c r="C33" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F33" s="22" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
@@ -22160,21 +22051,21 @@
       </c>
       <c r="C34" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F34" s="22" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
@@ -22186,21 +22077,21 @@
       </c>
       <c r="C35" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F35" s="22" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
@@ -22212,21 +22103,21 @@
       </c>
       <c r="C36" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F36" s="22" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
@@ -22238,21 +22129,21 @@
       </c>
       <c r="C37" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F37" s="22" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
@@ -22260,25 +22151,25 @@
         <v>31</v>
       </c>
       <c r="B38" s="22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C38" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D38" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E38" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F38" s="22" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
@@ -22286,25 +22177,25 @@
         <v>32</v>
       </c>
       <c r="B39" s="22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C39" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D39" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E39" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F39" s="22" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
@@ -22312,25 +22203,25 @@
         <v>33</v>
       </c>
       <c r="B40" s="22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D40" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E40" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F40" s="22" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
@@ -22338,520 +22229,292 @@
         <v>34</v>
       </c>
       <c r="B41" s="22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
+          <t>SYBMS (Marketing)</t>
         </is>
       </c>
       <c r="D41" s="22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Commerce</t>
         </is>
       </c>
       <c r="E41" s="22" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Planning &amp; Engagement of Co-curicular Activities (CC)</t>
         </is>
       </c>
       <c r="F41" s="22" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="22" t="n">
         <v>35</v>
       </c>
-      <c r="B42" s="22" t="n">
-        <v>7</v>
-      </c>
+      <c r="B42" s="22" t="n"/>
       <c r="C42" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.Sc (Biotechnology)</t>
-        </is>
-      </c>
-      <c r="D42" s="22" t="inlineStr">
-        <is>
-          <t>Biotechnology</t>
-        </is>
-      </c>
-      <c r="E42" s="22" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="F42" s="22" t="n">
-        <v>40</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="n"/>
+      <c r="E42" s="22" t="n"/>
+      <c r="F42" s="22" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="22" t="n">
         <v>36</v>
       </c>
-      <c r="B43" s="22" t="n">
-        <v>7</v>
-      </c>
+      <c r="B43" s="22" t="n"/>
       <c r="C43" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D43" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E43" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F43" s="22" t="n">
-        <v>1</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D43" s="22" t="n"/>
+      <c r="E43" s="22" t="n"/>
+      <c r="F43" s="22" t="n"/>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="22" t="n">
         <v>37</v>
       </c>
-      <c r="B44" s="22" t="n">
-        <v>7</v>
-      </c>
+      <c r="B44" s="22" t="n"/>
       <c r="C44" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D44" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E44" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F44" s="22" t="n">
-        <v>2</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D44" s="22" t="n"/>
+      <c r="E44" s="22" t="n"/>
+      <c r="F44" s="22" t="n"/>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="22" t="n">
         <v>38</v>
       </c>
-      <c r="B45" s="22" t="n">
-        <v>7</v>
-      </c>
+      <c r="B45" s="22" t="n"/>
       <c r="C45" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D45" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E45" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F45" s="22" t="n">
-        <v>3</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="n"/>
+      <c r="E45" s="22" t="n"/>
+      <c r="F45" s="22" t="n"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="22" t="n">
         <v>39</v>
       </c>
-      <c r="B46" s="22" t="n">
-        <v>7</v>
-      </c>
+      <c r="B46" s="22" t="n"/>
       <c r="C46" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D46" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E46" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F46" s="22" t="n">
-        <v>4</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D46" s="22" t="n"/>
+      <c r="E46" s="22" t="n"/>
+      <c r="F46" s="22" t="n"/>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="22" t="n">
         <v>40</v>
       </c>
-      <c r="B47" s="22" t="n">
-        <v>7</v>
-      </c>
+      <c r="B47" s="22" t="n"/>
       <c r="C47" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D47" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E47" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F47" s="22" t="n">
-        <v>5</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D47" s="22" t="n"/>
+      <c r="E47" s="22" t="n"/>
+      <c r="F47" s="22" t="n"/>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="22" t="n">
         <v>41</v>
       </c>
-      <c r="B48" s="22" t="n">
-        <v>7</v>
-      </c>
+      <c r="B48" s="22" t="n"/>
       <c r="C48" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D48" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E48" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F48" s="22" t="n">
-        <v>6</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D48" s="22" t="n"/>
+      <c r="E48" s="22" t="n"/>
+      <c r="F48" s="22" t="n"/>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="22" t="n">
         <v>42</v>
       </c>
-      <c r="B49" s="22" t="n">
-        <v>7</v>
-      </c>
+      <c r="B49" s="22" t="n"/>
       <c r="C49" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D49" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E49" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F49" s="22" t="n">
-        <v>7</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D49" s="22" t="n"/>
+      <c r="E49" s="22" t="n"/>
+      <c r="F49" s="22" t="n"/>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="22" t="n">
         <v>43</v>
       </c>
-      <c r="B50" s="22" t="n">
-        <v>7</v>
-      </c>
+      <c r="B50" s="22" t="n"/>
       <c r="C50" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D50" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E50" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F50" s="22" t="n">
-        <v>8</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D50" s="22" t="n"/>
+      <c r="E50" s="22" t="n"/>
+      <c r="F50" s="22" t="n"/>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="22" t="n">
         <v>44</v>
       </c>
-      <c r="B51" s="22" t="n">
-        <v>7</v>
-      </c>
+      <c r="B51" s="22" t="n"/>
       <c r="C51" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D51" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E51" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F51" s="22" t="n">
-        <v>9</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D51" s="22" t="n"/>
+      <c r="E51" s="22" t="n"/>
+      <c r="F51" s="22" t="n"/>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="22" t="n">
         <v>45</v>
       </c>
-      <c r="B52" s="22" t="n">
-        <v>7</v>
-      </c>
+      <c r="B52" s="22" t="n"/>
       <c r="C52" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D52" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E52" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F52" s="22" t="n">
-        <v>10</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D52" s="22" t="n"/>
+      <c r="E52" s="22" t="n"/>
+      <c r="F52" s="22" t="n"/>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="22" t="n">
         <v>46</v>
       </c>
-      <c r="B53" s="22" t="n">
-        <v>7</v>
-      </c>
+      <c r="B53" s="22" t="n"/>
       <c r="C53" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D53" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E53" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F53" s="22" t="n">
-        <v>11</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D53" s="22" t="n"/>
+      <c r="E53" s="22" t="n"/>
+      <c r="F53" s="22" t="n"/>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="22" t="n">
         <v>47</v>
       </c>
-      <c r="B54" s="22" t="n">
-        <v>7</v>
-      </c>
+      <c r="B54" s="22" t="n"/>
       <c r="C54" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D54" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E54" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F54" s="22" t="n">
-        <v>12</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D54" s="22" t="n"/>
+      <c r="E54" s="22" t="n"/>
+      <c r="F54" s="22" t="n"/>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="22" t="n">
         <v>48</v>
       </c>
-      <c r="B55" s="22" t="n">
-        <v>7</v>
-      </c>
+      <c r="B55" s="22" t="n"/>
       <c r="C55" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D55" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E55" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F55" s="22" t="n">
-        <v>13</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D55" s="22" t="n"/>
+      <c r="E55" s="22" t="n"/>
+      <c r="F55" s="22" t="n"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="22" t="n">
         <v>49</v>
       </c>
-      <c r="B56" s="22" t="n">
-        <v>7</v>
-      </c>
+      <c r="B56" s="22" t="n"/>
       <c r="C56" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D56" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E56" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F56" s="22" t="n">
-        <v>14</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D56" s="22" t="n"/>
+      <c r="E56" s="22" t="n"/>
+      <c r="F56" s="22" t="n"/>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="B57" s="22" t="n">
-        <v>7</v>
-      </c>
+      <c r="B57" s="22" t="n"/>
       <c r="C57" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D57" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E57" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F57" s="22" t="n">
-        <v>15</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D57" s="22" t="n"/>
+      <c r="E57" s="22" t="n"/>
+      <c r="F57" s="22" t="n"/>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="22" t="n">
         <v>51</v>
       </c>
-      <c r="B58" s="22" t="n">
-        <v>7</v>
-      </c>
+      <c r="B58" s="22" t="n"/>
       <c r="C58" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D58" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E58" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F58" s="22" t="n">
-        <v>16</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D58" s="22" t="n"/>
+      <c r="E58" s="22" t="n"/>
+      <c r="F58" s="22" t="n"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="22" t="n">
         <v>52</v>
       </c>
-      <c r="B59" s="22" t="n">
-        <v>7</v>
-      </c>
+      <c r="B59" s="22" t="n"/>
       <c r="C59" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D59" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E59" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F59" s="22" t="n">
-        <v>17</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D59" s="22" t="n"/>
+      <c r="E59" s="22" t="n"/>
+      <c r="F59" s="22" t="n"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="22" t="n">
         <v>53</v>
       </c>
-      <c r="B60" s="22" t="n">
-        <v>7</v>
-      </c>
+      <c r="B60" s="22" t="n"/>
       <c r="C60" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D60" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E60" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F60" s="22" t="n">
-        <v>18</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D60" s="22" t="n"/>
+      <c r="E60" s="22" t="n"/>
+      <c r="F60" s="22" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A7:F60"/>
@@ -22939,7 +22602,7 @@
         </is>
       </c>
       <c r="D4" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
@@ -22947,7 +22610,7 @@
         </is>
       </c>
       <c r="F4" s="12" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
@@ -23006,833 +22669,449 @@
       <c r="A8" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B8" s="22" t="n"/>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>19</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="n"/>
+      <c r="E8" s="22" t="n"/>
+      <c r="F8" s="22" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B9" s="22" t="n"/>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="n">
-        <v>20</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="22" t="n"/>
+      <c r="F9" s="22" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B10" s="22" t="n"/>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>21</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="n"/>
+      <c r="E10" s="22" t="n"/>
+      <c r="F10" s="22" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B11" s="22" t="n"/>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>22</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="22" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B12" s="22" t="n"/>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E12" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F12" s="22" t="n">
-        <v>23</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="n"/>
+      <c r="E12" s="22" t="n"/>
+      <c r="F12" s="22" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B13" s="22" t="n"/>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F13" s="22" t="n">
-        <v>24</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="22" t="n"/>
+      <c r="F13" s="22" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B14" s="22" t="n"/>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="n">
-        <v>25</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="n"/>
+      <c r="E14" s="22" t="n"/>
+      <c r="F14" s="22" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B15" s="22" t="n"/>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="n">
-        <v>26</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="22" t="n"/>
+      <c r="F15" s="22" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="22" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B16" s="22" t="n"/>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D16" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="n">
-        <v>27</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="22" t="n"/>
+      <c r="F16" s="22" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B17" s="22" t="n"/>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D17" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="n">
-        <v>28</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="n"/>
+      <c r="E17" s="22" t="n"/>
+      <c r="F17" s="22" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B18" s="22" t="n"/>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D18" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="n">
-        <v>29</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="22" t="n"/>
+      <c r="F18" s="22" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B19" s="22" t="n"/>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E19" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F19" s="22" t="n">
-        <v>30</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="22" t="n"/>
+      <c r="F19" s="22" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B20" s="22" t="n"/>
       <c r="C20" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E20" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F20" s="22" t="n">
-        <v>31</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="22" t="n"/>
+      <c r="F20" s="22" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B21" s="22" t="n"/>
       <c r="C21" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D21" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E21" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F21" s="22" t="n">
-        <v>32</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="22" t="n"/>
+      <c r="F21" s="22" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B22" s="22" t="n"/>
       <c r="C22" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="n">
-        <v>33</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="22" t="n"/>
+      <c r="F22" s="22" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="22" t="n">
         <v>16</v>
       </c>
-      <c r="B23" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B23" s="22" t="n"/>
       <c r="C23" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D23" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E23" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="n">
-        <v>34</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="22" t="n"/>
+      <c r="F23" s="22" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="B24" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B24" s="22" t="n"/>
       <c r="C24" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D24" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E24" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F24" s="22" t="n">
-        <v>35</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="22" t="n"/>
+      <c r="F24" s="22" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="B25" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B25" s="22" t="n"/>
       <c r="C25" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D25" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E25" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F25" s="22" t="n">
-        <v>36</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="22" t="n"/>
+      <c r="F25" s="22" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="22" t="n">
         <v>19</v>
       </c>
-      <c r="B26" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B26" s="22" t="n"/>
       <c r="C26" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D26" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E26" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F26" s="22" t="n">
-        <v>37</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="22" t="n"/>
+      <c r="F26" s="22" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="B27" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B27" s="22" t="n"/>
       <c r="C27" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E27" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F27" s="22" t="n">
-        <v>38</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="22" t="n"/>
+      <c r="F27" s="22" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="B28" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B28" s="22" t="n"/>
       <c r="C28" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D28" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E28" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F28" s="22" t="n">
-        <v>39</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="22" t="n"/>
+      <c r="F28" s="22" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="22" t="n">
         <v>22</v>
       </c>
-      <c r="B29" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B29" s="22" t="n"/>
       <c r="C29" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D29" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E29" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F29" s="22" t="n">
-        <v>40</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="n"/>
+      <c r="E29" s="22" t="n"/>
+      <c r="F29" s="22" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="22" t="n">
         <v>23</v>
       </c>
-      <c r="B30" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B30" s="22" t="n"/>
       <c r="C30" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D30" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E30" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F30" s="22" t="n">
-        <v>41</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="22" t="n"/>
+      <c r="F30" s="22" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="22" t="n">
         <v>24</v>
       </c>
-      <c r="B31" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B31" s="22" t="n"/>
       <c r="C31" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D31" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E31" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F31" s="22" t="n">
-        <v>42</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="n"/>
+      <c r="E31" s="22" t="n"/>
+      <c r="F31" s="22" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="B32" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B32" s="22" t="n"/>
       <c r="C32" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D32" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E32" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F32" s="22" t="n">
-        <v>43</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="22" t="n"/>
+      <c r="F32" s="22" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="22" t="n">
         <v>26</v>
       </c>
-      <c r="B33" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B33" s="22" t="n"/>
       <c r="C33" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D33" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E33" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F33" s="22" t="n">
-        <v>44</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="22" t="n"/>
+      <c r="F33" s="22" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="22" t="n">
         <v>27</v>
       </c>
-      <c r="B34" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B34" s="22" t="n"/>
       <c r="C34" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D34" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E34" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F34" s="22" t="n">
-        <v>45</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="n"/>
+      <c r="E34" s="22" t="n"/>
+      <c r="F34" s="22" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="22" t="n">
         <v>28</v>
       </c>
-      <c r="B35" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B35" s="22" t="n"/>
       <c r="C35" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D35" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E35" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F35" s="22" t="n">
-        <v>46</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="n"/>
+      <c r="E35" s="22" t="n"/>
+      <c r="F35" s="22" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="22" t="n">
         <v>29</v>
       </c>
-      <c r="B36" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B36" s="22" t="n"/>
       <c r="C36" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D36" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E36" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F36" s="22" t="n">
-        <v>47</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="n"/>
+      <c r="E36" s="22" t="n"/>
+      <c r="F36" s="22" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="B37" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B37" s="22" t="n"/>
       <c r="C37" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D37" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E37" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F37" s="22" t="n">
-        <v>48</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="n"/>
+      <c r="E37" s="22" t="n"/>
+      <c r="F37" s="22" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="22" t="n">
         <v>31</v>
       </c>
-      <c r="B38" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B38" s="22" t="n"/>
       <c r="C38" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D38" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E38" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F38" s="22" t="n">
-        <v>49</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="n"/>
+      <c r="E38" s="22" t="n"/>
+      <c r="F38" s="22" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="22" t="n">
         <v>32</v>
       </c>
-      <c r="B39" s="22" t="n">
-        <v>8</v>
-      </c>
+      <c r="B39" s="22" t="n"/>
       <c r="C39" s="22" t="inlineStr">
         <is>
-          <t>F.Y.B.A</t>
-        </is>
-      </c>
-      <c r="D39" s="22" t="inlineStr">
-        <is>
-          <t>Arts</t>
-        </is>
-      </c>
-      <c r="E39" s="22" t="inlineStr">
-        <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="F39" s="22" t="n">
-        <v>50</v>
-      </c>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="n"/>
+      <c r="E39" s="22" t="n"/>
+      <c r="F39" s="22" t="n"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="22" t="n">
